--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-dispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="526">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:31:13+00:00</t>
+    <t>2026-10-15T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -911,7 +911,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260916095452</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -967,137 +967,6 @@
   </si>
   <si>
     <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.id</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.extension</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
-  </si>
-  <si>
-    <t>Not allowed to be used in this context</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-edqm|2.2.0</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>MedicationDispense.quantity.code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -2086,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO78"/>
+  <dimension ref="A1:AO71"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.29296875" customWidth="true" bestFit="true"/>
@@ -6008,13 +5877,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>309</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6065,7 +5934,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>232</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6077,13 +5946,13 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
@@ -6092,26 +5961,26 @@
         <v>79</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>79</v>
+        <v>311</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -6120,20 +5989,18 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>136</v>
+        <v>314</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>79</v>
@@ -6170,54 +6037,54 @@
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>233</v>
+        <v>316</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>79</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6237,23 +6104,19 @@
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
@@ -6301,7 +6164,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6316,27 +6179,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>79</v>
+        <v>322</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>79</v>
+        <v>317</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6347,36 +6210,32 @@
         <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>321</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="Q37" t="s" s="2">
-        <v>322</v>
-      </c>
+      <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
         <v>79</v>
       </c>
@@ -6396,31 +6255,31 @@
         <v>79</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>323</v>
+        <v>79</v>
       </c>
       <c r="Z37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6438,24 +6297,24 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>79</v>
+        <v>328</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6466,7 +6325,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
@@ -6475,21 +6334,19 @@
         <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>229</v>
+        <v>331</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>331</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6513,11 +6370,13 @@
         <v>79</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>332</v>
+        <v>79</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>79</v>
@@ -6535,13 +6394,13 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
@@ -6559,10 +6418,10 @@
         <v>79</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
@@ -6581,7 +6440,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>79</v>
@@ -6590,21 +6449,19 @@
         <v>79</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>103</v>
+        <v>337</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>339</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>79</v>
       </c>
@@ -6652,34 +6509,34 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>335</v>
       </c>
     </row>
     <row r="40">
@@ -6698,7 +6555,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>79</v>
@@ -6707,23 +6564,21 @@
         <v>79</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>109</v>
+        <v>344</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O40" t="s" s="2">
         <v>347</v>
       </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>79</v>
       </c>
@@ -6771,13 +6626,13 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>79</v>
@@ -6789,7 +6644,7 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>79</v>
@@ -6798,15 +6653,15 @@
         <v>79</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>335</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6829,13 +6684,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>301</v>
+        <v>229</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>351</v>
+        <v>230</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>352</v>
+        <v>231</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6886,7 +6741,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>232</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6898,13 +6753,13 @@
         <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6913,26 +6768,26 @@
         <v>79</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>354</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6941,18 +6796,20 @@
         <v>79</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>356</v>
+        <v>135</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>357</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>79</v>
@@ -6989,86 +6846,90 @@
         <v>79</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>355</v>
+        <v>236</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>359</v>
+        <v>233</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>356</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>363</v>
+        <v>239</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>79</v>
       </c>
@@ -7116,42 +6977,42 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>362</v>
+        <v>241</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>366</v>
+        <v>132</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>79</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7171,19 +7032,21 @@
         <v>79</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>256</v>
+        <v>353</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
       </c>
@@ -7231,7 +7094,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7249,24 +7112,24 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>371</v>
+        <v>79</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7277,7 +7140,7 @@
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>79</v>
@@ -7286,19 +7149,21 @@
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>374</v>
+        <v>229</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>376</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7346,13 +7211,13 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>79</v>
@@ -7364,24 +7229,24 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7401,19 +7266,23 @@
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>380</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>79</v>
       </c>
@@ -7437,13 +7306,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>79</v>
+        <v>371</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7461,7 +7330,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7476,10 +7345,10 @@
         <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>383</v>
+        <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -7488,15 +7357,15 @@
         <v>79</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7507,7 +7376,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>79</v>
@@ -7516,20 +7385,18 @@
         <v>79</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>387</v>
+        <v>229</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>79</v>
@@ -7578,13 +7445,13 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>79</v>
@@ -7596,7 +7463,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7605,15 +7472,15 @@
         <v>79</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>79</v>
+        <v>374</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7633,19 +7500,23 @@
         <v>79</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>229</v>
+        <v>380</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>230</v>
+        <v>381</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>384</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7693,7 +7564,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>232</v>
+        <v>385</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7705,13 +7576,13 @@
         <v>79</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>233</v>
+        <v>386</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7725,21 +7596,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7748,19 +7619,19 @@
         <v>79</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>388</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>136</v>
+        <v>389</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>235</v>
+        <v>390</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>138</v>
+        <v>391</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7786,49 +7657,49 @@
         <v>79</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>79</v>
+        <v>392</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>79</v>
+        <v>393</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>236</v>
+        <v>394</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>233</v>
+        <v>395</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7837,50 +7708,50 @@
         <v>79</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>396</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="J50" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>135</v>
+        <v>182</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>239</v>
+        <v>398</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>240</v>
+        <v>399</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>138</v>
+        <v>400</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>144</v>
+        <v>401</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>79</v>
@@ -7905,13 +7776,13 @@
         <v>79</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>79</v>
+        <v>402</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>79</v>
+        <v>403</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>79</v>
@@ -7929,25 +7800,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>241</v>
+        <v>404</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>132</v>
+        <v>405</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7956,15 +7827,15 @@
         <v>79</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7987,17 +7858,17 @@
         <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>396</v>
+        <v>182</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -8022,13 +7893,13 @@
         <v>79</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>79</v>
+        <v>411</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>79</v>
+        <v>412</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>79</v>
@@ -8046,7 +7917,7 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8064,7 +7935,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -8073,15 +7944,15 @@
         <v>79</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>402</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8104,17 +7975,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>79</v>
@@ -8139,13 +8012,13 @@
         <v>79</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>79</v>
+        <v>422</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>79</v>
@@ -8163,7 +8036,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8181,7 +8054,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -8190,15 +8063,15 @@
         <v>79</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>408</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>409</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8221,20 +8094,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>182</v>
+        <v>427</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>79</v>
       </c>
@@ -8258,13 +8127,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>414</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>415</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -8282,7 +8151,7 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8300,7 +8169,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>401</v>
+        <v>79</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8309,15 +8178,15 @@
         <v>79</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8337,16 +8206,16 @@
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
         <v>229</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>419</v>
+        <v>230</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>420</v>
+        <v>231</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8397,7 +8266,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>421</v>
+        <v>232</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8409,13 +8278,13 @@
         <v>79</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>401</v>
+        <v>233</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -8424,26 +8293,26 @@
         <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>79</v>
@@ -8452,23 +8321,21 @@
         <v>79</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>423</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>424</v>
+        <v>136</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>425</v>
+        <v>235</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>79</v>
       </c>
@@ -8504,37 +8371,37 @@
         <v>79</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>236</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>429</v>
+        <v>233</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -8548,10 +8415,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8574,18 +8441,18 @@
         <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>431</v>
+        <v>182</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>436</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>437</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>79</v>
       </c>
@@ -8612,10 +8479,10 @@
         <v>176</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>79</v>
@@ -8633,7 +8500,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8651,7 +8518,7 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>438</v>
+        <v>79</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>79</v>
@@ -8660,15 +8527,15 @@
         <v>79</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8691,19 +8558,19 @@
         <v>90</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>182</v>
+        <v>443</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8728,13 +8595,13 @@
         <v>79</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>445</v>
+        <v>79</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>446</v>
+        <v>79</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>79</v>
@@ -8752,7 +8619,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8770,7 +8637,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8810,17 +8677,19 @@
         <v>90</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>182</v>
+        <v>451</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>79</v>
@@ -8845,13 +8714,13 @@
         <v>79</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>454</v>
+        <v>79</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>455</v>
+        <v>79</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>79</v>
@@ -8927,19 +8796,19 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>182</v>
+        <v>460</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>79</v>
@@ -8964,31 +8833,31 @@
         <v>79</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="Z59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF59" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9006,24 +8875,24 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>468</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9034,7 +8903,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>79</v>
@@ -9046,16 +8915,20 @@
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>471</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>79</v>
       </c>
@@ -9109,7 +8982,7 @@
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>79</v>
@@ -9121,7 +8994,7 @@
         <v>79</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
@@ -9130,7 +9003,7 @@
         <v>79</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>474</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
@@ -9158,19 +9031,21 @@
         <v>79</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>229</v>
+        <v>301</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>230</v>
+        <v>476</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>231</v>
+        <v>477</v>
       </c>
       <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
       </c>
@@ -9218,7 +9093,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>232</v>
+        <v>479</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9230,13 +9105,13 @@
         <v>79</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>233</v>
+        <v>474</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
@@ -9250,21 +9125,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>79</v>
@@ -9276,17 +9151,15 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>135</v>
+        <v>223</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>136</v>
+        <v>481</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>79</v>
@@ -9323,43 +9196,43 @@
         <v>79</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>279</v>
+        <v>79</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>280</v>
+        <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>236</v>
+        <v>480</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>233</v>
+        <v>483</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>79</v>
+        <v>484</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9367,10 +9240,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9390,21 +9263,19 @@
         <v>79</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>182</v>
+        <v>229</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>478</v>
+        <v>230</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>479</v>
+        <v>231</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>480</v>
-      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>79</v>
       </c>
@@ -9428,13 +9299,13 @@
         <v>79</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>481</v>
+        <v>79</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>482</v>
+        <v>79</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>79</v>
@@ -9452,7 +9323,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>483</v>
+        <v>232</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9464,13 +9335,13 @@
         <v>79</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9479,26 +9350,26 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>484</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>79</v>
@@ -9507,23 +9378,21 @@
         <v>79</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>486</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>487</v>
+        <v>136</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>488</v>
+        <v>235</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>79</v>
       </c>
@@ -9571,25 +9440,25 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>491</v>
+        <v>236</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>467</v>
+        <v>233</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9598,50 +9467,50 @@
         <v>79</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>492</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>494</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>495</v>
+        <v>239</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>496</v>
+        <v>240</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>497</v>
+        <v>138</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>498</v>
+        <v>144</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>79</v>
@@ -9690,25 +9559,25 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>241</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>500</v>
+        <v>132</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
@@ -9717,15 +9586,15 @@
         <v>79</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>501</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9733,7 +9602,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -9745,23 +9614,19 @@
         <v>79</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>79</v>
       </c>
@@ -9809,10 +9674,10 @@
         <v>79</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>89</v>
@@ -9827,7 +9692,7 @@
         <v>79</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>79</v>
@@ -9836,15 +9701,15 @@
         <v>79</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>510</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9864,23 +9729,19 @@
         <v>79</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>515</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>79</v>
       </c>
@@ -9904,13 +9765,13 @@
         <v>79</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>79</v>
@@ -9928,7 +9789,7 @@
         <v>79</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -9946,24 +9807,24 @@
         <v>79</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>517</v>
+        <v>273</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>79</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>79</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9974,7 +9835,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>79</v>
@@ -9983,21 +9844,19 @@
         <v>79</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>301</v>
+        <v>182</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>521</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>79</v>
       </c>
@@ -10021,13 +9880,13 @@
         <v>79</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>79</v>
+        <v>503</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>79</v>
+        <v>504</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>79</v>
@@ -10045,13 +9904,13 @@
         <v>79</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>522</v>
+        <v>500</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>79</v>
@@ -10063,13 +9922,13 @@
         <v>79</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>79</v>
+        <v>506</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>79</v>
@@ -10077,10 +9936,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10091,7 +9950,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>79</v>
@@ -10103,13 +9962,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>223</v>
+        <v>508</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10160,13 +10019,13 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>79</v>
@@ -10178,13 +10037,13 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>79</v>
@@ -10192,21 +10051,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>79</v>
+        <v>514</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>79</v>
@@ -10218,15 +10077,17 @@
         <v>79</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>229</v>
+        <v>515</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>230</v>
+        <v>516</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>79</v>
@@ -10275,25 +10136,25 @@
         <v>79</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>232</v>
+        <v>513</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>233</v>
+        <v>519</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>79</v>
@@ -10307,14 +10168,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10333,16 +10194,16 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>135</v>
+        <v>521</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>136</v>
+        <v>522</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>235</v>
+        <v>523</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>138</v>
+        <v>524</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10392,7 +10253,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>236</v>
+        <v>520</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10404,13 +10265,13 @@
         <v>79</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>233</v>
+        <v>525</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
@@ -10419,819 +10280,6 @@
         <v>79</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="P72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AM72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AO76" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO77" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO78" t="s" s="2">
         <v>79</v>
       </c>
     </row>
